--- a/cfg/excel/lang_cfg.xlsx
+++ b/cfg/excel/lang_cfg.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Emanon\cfg\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Emanon\cfg\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1EEB2D-3C00-4DAC-BB11-3A7FF6C1036F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E046219E-397C-4CAC-882B-2F3FAB1D87E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="164">
   <si>
     <t>[TABLE_BEGIN]</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -743,6 +743,54 @@
   </si>
   <si>
     <t>Created&amp;Artistic by Shelton</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>password_title</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>密码验证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Password</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>パスワード</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>password_input_placeholder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请输入密码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enter password</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>パスワードを入力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>timer.refresh_complete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Refreshing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正在刷新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新中</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1120,21 +1168,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D44"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="59.75" customWidth="1"/>
-    <col min="3" max="3" width="57.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="75.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1148,7 +1196,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1162,7 +1210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1176,7 +1224,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -1190,7 +1238,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>146</v>
       </c>
@@ -1204,7 +1252,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>147</v>
       </c>
@@ -1218,7 +1266,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -1232,7 +1280,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>149</v>
       </c>
@@ -1246,7 +1294,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -1260,7 +1308,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -1274,7 +1322,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -1288,7 +1336,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>97</v>
       </c>
@@ -1302,7 +1350,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>98</v>
       </c>
@@ -1316,7 +1364,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -1330,7 +1378,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>51</v>
       </c>
@@ -1344,7 +1392,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>102</v>
       </c>
@@ -1358,7 +1406,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -1372,7 +1420,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -1386,7 +1434,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1400,7 +1448,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1414,7 +1462,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1428,7 +1476,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1442,7 +1490,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1456,7 +1504,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1470,7 +1518,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -1484,7 +1532,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -1498,7 +1546,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1512,7 +1560,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>54</v>
       </c>
@@ -1526,7 +1574,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>60</v>
       </c>
@@ -1540,7 +1588,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -1554,7 +1602,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>62</v>
       </c>
@@ -1568,7 +1616,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -1582,7 +1630,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -1596,7 +1644,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1610,7 +1658,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>72</v>
       </c>
@@ -1624,7 +1672,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>73</v>
       </c>
@@ -1638,7 +1686,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -1652,7 +1700,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>85</v>
       </c>
@@ -1666,7 +1714,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -1680,7 +1728,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="87.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="86.5" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>105</v>
       </c>
@@ -1694,7 +1742,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>123</v>
       </c>
@@ -1708,7 +1756,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="108.75" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" ht="106" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="3" t="s">
         <v>142</v>
       </c>
@@ -1722,8 +1770,50 @@
         <v>145</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>4</v>
       </c>
     </row>

--- a/cfg/excel/lang_cfg.xlsx
+++ b/cfg/excel/lang_cfg.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Emanon\cfg\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E046219E-397C-4CAC-882B-2F3FAB1D87E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2E4E64-8294-4516-A323-6F48762D9EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,11 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="164">
-  <si>
-    <t>[TABLE_BEGIN]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="162">
   <si>
     <t>文本id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -49,10 +45,6 @@
   </si>
   <si>
     <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[TABLE_END]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1168,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -1178,8 +1170,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -1187,13 +1188,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1201,265 +1202,265 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>58</v>
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
         <v>43</v>
       </c>
-      <c r="B11" t="s">
-        <v>50</v>
-      </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
         <v>11</v>
       </c>
-      <c r="B18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" t="s">
-        <v>16</v>
-      </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -1470,10 +1471,10 @@
         <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -1484,10 +1485,10 @@
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -1498,323 +1499,304 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
+        <v>148</v>
       </c>
       <c r="C26" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s">
-        <v>110</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" t="s">
         <v>39</v>
       </c>
-      <c r="B27" t="s">
-        <v>150</v>
-      </c>
-      <c r="C27" t="s">
-        <v>151</v>
-      </c>
       <c r="D27" t="s">
-        <v>151</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
         <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D28" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="D32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D35" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D36" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D39" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="86.5" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>90</v>
-      </c>
-      <c r="B40" t="s">
-        <v>91</v>
-      </c>
-      <c r="C40" t="s">
-        <v>92</v>
-      </c>
-      <c r="D40" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="86.5" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="B41" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="106" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="3" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="106" x14ac:dyDescent="0.55000000000000004">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C46" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/cfg/excel/lang_cfg.xlsx
+++ b/cfg/excel/lang_cfg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Emanon\cfg\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2E4E64-8294-4516-A323-6F48762D9EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BDDA69C-B448-48C8-ABE6-C672D427DC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8350" yWindow="1490" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="234">
   <si>
     <t>文本id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,10 +68,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Last Updated:{0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dailty_popup_title</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -80,10 +76,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Please choose your language:</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>请选择你的语言：</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -92,10 +84,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>welcome to log in</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>btn_ok</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -104,10 +92,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Confirm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>tab_progress</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -116,10 +100,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Progress</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>tab_article</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -152,22 +132,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Article</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Game</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gallery</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>About</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>index_title</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -176,10 +140,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Memories of Emanon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>footer_update_time</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -192,10 +152,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Artistic by Cry</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>index_year_progress</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -212,18 +168,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Year progress</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Month progress</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Day progress</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>年进度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -236,10 +180,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Refresh in {0}m {1}s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>刷新时间剩余 {0}m {1}s</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -252,10 +192,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CRT Simulation</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CRT效果模拟</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -284,14 +220,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{0} hours,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>equivalent to {0} days,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{0}小时，</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -304,10 +232,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Games are not life, but I've been playing for:</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>game_roll_btn</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -340,22 +264,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Random games</t>
-  </si>
-  <si>
-    <t>Sort by subjective game ratings</t>
-  </si>
-  <si>
-    <t>Sort by game genre</t>
-  </si>
-  <si>
-    <t>Sort by game duration</t>
-  </si>
-  <si>
-    <t>approximately {0} years.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>相当于{0}年。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -376,14 +284,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Previous</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Next</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>original_image</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -392,22 +292,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>originnal image</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>This progress bar indicates how much of the year has passed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>This progress bar indicates how much of the month has passed.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>This progress bar indicates how much of the day has passed.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>index_day_tips</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -436,10 +320,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>After the countdown ends, all progress bars will be refreshed.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>倒计时结束后，所有的进度条都将被刷新</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -457,46 +337,13 @@
     <t>ギャラリー</t>
   </si>
   <si>
-    <t>について</t>
-  </si>
-  <si>
-    <t>前回更新：{0}</t>
-  </si>
-  <si>
-    <t>CRT 効果シミュレーション</t>
-  </si>
-  <si>
-    <t>{0} 時間、</t>
-  </si>
-  <si>
-    <t>{0} 日に相当し、</t>
-  </si>
-  <si>
-    <t>{0} 年に相当します。</t>
-  </si>
-  <si>
-    <t>ゲームは人生ではありませんが、私はすでにプレイしています：</t>
-  </si>
-  <si>
     <t>ランダムゲーム</t>
   </si>
   <si>
-    <t>主観的なゲーム評価で並べ替える</t>
-  </si>
-  <si>
-    <t>ゲームジャンルで並べ替える</t>
-  </si>
-  <si>
-    <t>ゲームのプレイ時間で並べ替える</t>
-  </si>
-  <si>
     <t>前のページ</t>
   </si>
   <si>
     <t>次のページ</t>
-  </si>
-  <si>
-    <t>オリジナル画像</t>
   </si>
   <si>
     <t>thanks_project</t>
@@ -546,243 +393,524 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Hi! I'm Shelton Chu, a game designer and artist from China.
-The best way to get to know me better is to browse through this website.
-To start your exploration, you can take a look at the navigation bar at the top. I hope you have a pleasant browsing experience here!
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>update_info</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>article_title</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>game_title</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gallery_title</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>about_title</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>由 Shelton 进行站点创建与艺术化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>password_title</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>密码验证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>password_input_placeholder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请输入密码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>timer.refresh_complete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正在刷新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>message_title</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>留言板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tab_message</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_form_title</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>写下你的留言</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_nickname_label</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>昵称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_nickname_placeholder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_content_label</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>留言内容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_content_placeholder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>写点什么吧…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你的昵称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_submit_btn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发送</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_list_title</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>留言列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_refresh_btn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刷新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_loading</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正在加载留言…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_empty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂无留言，和我说点什么！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_error</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加载留言失败，请稍后再试。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_load_more</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加载更多</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_warn_nickname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请输入昵称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_warn_content</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请输入留言内容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_success_title</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>留言已发送！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_submit_error</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>发送失败，请稍后再试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最近更新
+版本号：14.0.0
+发布日期：2026年3月12日
+新增留言板功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Memories of Emanon</t>
+  </si>
+  <si>
+    <t>Articles</t>
+  </si>
+  <si>
+    <t>Games</t>
+  </si>
+  <si>
+    <t>Gallery</t>
+  </si>
+  <si>
+    <t>About</t>
+  </si>
+  <si>
+    <t>Year Progress</t>
+  </si>
+  <si>
+    <t>Month Progress</t>
+  </si>
+  <si>
+    <t>Day Progress</t>
+  </si>
+  <si>
+    <t>This progress bar shows how much of the current year has passed.</t>
+  </si>
+  <si>
+    <t>This progress bar shows how much of the current month has passed.</t>
+  </si>
+  <si>
+    <t>This progress bar shows how much of today has passed.</t>
+  </si>
+  <si>
+    <t>Refreshing in {0}m {1}s</t>
+  </si>
+  <si>
+    <t>When the countdown ends, all progress bars will be refreshed.</t>
+  </si>
+  <si>
+    <t>Welcome</t>
+  </si>
+  <si>
+    <t>Please select your language:</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Progress</t>
+  </si>
+  <si>
+    <t>Last updated: {0}</t>
+  </si>
+  <si>
+    <t>Site created and curated by Shelton</t>
+  </si>
+  <si>
+    <t>Artwork by Cry</t>
+  </si>
+  <si>
+    <t>CRT Effect Simulation</t>
+  </si>
+  <si>
+    <t>{0} hours,</t>
+  </si>
+  <si>
+    <t>equivalent to {0} days,</t>
+  </si>
+  <si>
+    <t>equivalent to {0} years.</t>
+  </si>
+  <si>
+    <t>Games are not life, but I have already played for:</t>
+  </si>
+  <si>
+    <t>Random Game</t>
+  </si>
+  <si>
+    <t>Sort by Personal Rating</t>
+  </si>
+  <si>
+    <t>Sort by Genre</t>
+  </si>
+  <si>
+    <t>Sort by Playtime</t>
+  </si>
+  <si>
+    <t>Previous Page</t>
+  </si>
+  <si>
+    <t>Next Page</t>
+  </si>
+  <si>
+    <t>Original Image</t>
   </si>
   <si>
     <t>Thanks to the following projects:</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> こんにちは！私はシェルトン</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">チューです。中国出身のゲームデザイナーとアーティストです。
-私をもっと深く知るには、このウェブサイトを見て回るのが一番いい方法です。
-探検を始めるには、トップのナビゲーションバーを見てみてください。ここで楽しいブラウジング体験をしていただければ幸いです！
-</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Password Verification</t>
+  </si>
+  <si>
+    <t>Enter password</t>
+  </si>
+  <si>
+    <t>Refreshing</t>
+  </si>
+  <si>
+    <t>Message Board</t>
+  </si>
+  <si>
+    <t>Leave a Message</t>
+  </si>
+  <si>
+    <t>Nickname</t>
+  </si>
+  <si>
+    <t>Your nickname</t>
+  </si>
+  <si>
+    <t>Message</t>
+  </si>
+  <si>
+    <t>Write something…</t>
+  </si>
+  <si>
+    <t>Send</t>
+  </si>
+  <si>
+    <t>Message List</t>
+  </si>
+  <si>
+    <t>Refresh</t>
+  </si>
+  <si>
+    <t>Loading messages…</t>
+  </si>
+  <si>
+    <t>No messages yet. Say something!</t>
+  </si>
+  <si>
+    <t>Failed to load messages. Please try again later.</t>
+  </si>
+  <si>
+    <t>Load More</t>
+  </si>
+  <si>
+    <t>Please enter a nickname</t>
+  </si>
+  <si>
+    <t>Please enter a message</t>
+  </si>
+  <si>
+    <t>Message sent!</t>
+  </si>
+  <si>
+    <t>Failed to send message. Please try again later.</t>
+  </si>
+  <si>
+    <t>Recent Updates
+Version: 14.0.0
+Release Date: March 12, 2026
+Added: Message Board Feature</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hi! I'm Shelton Chu, a game designer and artist from China. 
+The best way to get to know me is by exploring this website. 
+To start your journey, check out the navigation bar above. Hope you enjoy your time here!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>エマノンの記憶</t>
+  </si>
+  <si>
+    <t>このサイトについて</t>
+  </si>
+  <si>
+    <t>年の進捗</t>
+  </si>
+  <si>
+    <t>月の進捗</t>
+  </si>
+  <si>
+    <t>今日の進捗</t>
+  </si>
+  <si>
+    <t>このプログレスバーは、今年がどれくらい経過したかを示します。</t>
+  </si>
+  <si>
+    <t>このプログレスバーは、今月がどれくらい経過したかを示します。</t>
+  </si>
+  <si>
+    <t>このプログレスバーは、今日がどれくらい経過したかを示します。</t>
+  </si>
+  <si>
+    <t>{0}分 {1}秒後に更新</t>
+  </si>
+  <si>
+    <t>カウントダウンが終了すると、すべての進捗バーが更新されます。</t>
+  </si>
+  <si>
+    <t>ようこそ</t>
+  </si>
+  <si>
+    <t>言語を選択してください：</t>
+  </si>
+  <si>
+    <t>確定</t>
+  </si>
+  <si>
+    <t>進捗</t>
+  </si>
+  <si>
+    <t>最終更新：{0}</t>
+  </si>
+  <si>
+    <t>サイト制作・運営：Shelton</t>
+  </si>
+  <si>
+    <t>アート制作：Cry</t>
+  </si>
+  <si>
+    <t>CRTエフェクトシミュレーション</t>
+  </si>
+  <si>
+    <t>{0}時間、</t>
+  </si>
+  <si>
+    <t>約{0}日、</t>
+  </si>
+  <si>
+    <t>約{0}年。</t>
+  </si>
+  <si>
+    <t>ゲームは人生ではない。でも私はすでに：</t>
+  </si>
+  <si>
+    <t>個人的評価順</t>
+  </si>
+  <si>
+    <t>ジャンル順</t>
+  </si>
+  <si>
+    <t>プレイ時間順</t>
+  </si>
+  <si>
+    <t>元画像</t>
   </si>
   <si>
     <t>以下のプロジェクトに感謝します：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>年の進行状況</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>月の進行状況</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日の進行状況</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>この進捗バーは今年がどれだけ経過したかを示しています</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>この進捗バーは今月がどれだけ経過したかを示しています</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>この進捗バーは今日がどれだけ経過したかを示しています</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新まであと {0} 分 {1} 秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>カウントダウンが終了したら、すべての進捗バーが更新されます</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ログインを歓迎します</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>あなたの言語を選択してください：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>確認する</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>進捗バー</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update_info</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最近更新
-版本号：13.0.0
-发布日期：2025-04-01
-核心更新：
-多语言系统增强
-• 新增日语语言支持（801bda8）
-• 扩展基础语言框架（7ec452e）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Recent Update
-Version Number: 13.0.0
-Release Date: April 1, 2025
-Core Updates:
-Enhancement of the Multilingual System
-• Added Japanese language support (801bda8)
-• Extended the basic language framework (7ec452e)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">最近のアップデート
-バージョン番号：13.0.0
-リリース日：2025 年 4 月 1 日
-核心アップデート：
-多言語システムの強化
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>・日本語の言語サポートを新たに追加しました</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">（801bda8）
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>・基本的な言語フレームワークを拡張しました</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（7ec452e）</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>article_title</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>game_title</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gallery_title</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>about_title</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>由 Shelton 进行站点创建与艺术化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Created&amp;Artistic by Shelton</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>password_title</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>密码验证</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Password</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>パスワード</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>password_input_placeholder</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>请输入密码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enter password</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>パスワードを入力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>timer.refresh_complete</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Refreshing</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>正在刷新</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>パスワード認証</t>
+  </si>
+  <si>
+    <t>パスワードを入力してください</t>
   </si>
   <si>
     <t>更新中</t>
+  </si>
+  <si>
+    <t>メッセージボード</t>
+  </si>
+  <si>
+    <t>メッセージを書く</t>
+  </si>
+  <si>
+    <t>ニックネーム</t>
+  </si>
+  <si>
+    <t>ニックネームを入力</t>
+  </si>
+  <si>
+    <t>メッセージ</t>
+  </si>
+  <si>
+    <t>何か書いてみましょう…</t>
+  </si>
+  <si>
+    <t>送信</t>
+  </si>
+  <si>
+    <t>メッセージ一覧</t>
+  </si>
+  <si>
+    <t>更新</t>
+  </si>
+  <si>
+    <t>メッセージを読み込み中…</t>
+  </si>
+  <si>
+    <t>まだメッセージがありません。ぜひ書いてください！</t>
+  </si>
+  <si>
+    <t>メッセージの読み込みに失敗しました。後でもう一度お試しください。</t>
+  </si>
+  <si>
+    <t>さらに読み込む</t>
+  </si>
+  <si>
+    <t>ニックネームを入力してください</t>
+  </si>
+  <si>
+    <t>メッセージ内容を入力してください</t>
+  </si>
+  <si>
+    <t>送信完了！</t>
+  </si>
+  <si>
+    <t>送信に失敗しました。後でもう一度お試しください。</t>
+  </si>
+  <si>
+    <t>こんにちは！私はShelton Chu、中国出身のゲームプランナー兼アーティストです。
+私をより深く知る一番の方法は、このサイトをゆっくりと閲覧することです。
+まずは上のナビゲーションバーから探索してみてください。このサイトでの時間を楽しんでいただければ嬉しいです！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最近の更新
+バージョン：14.0.0
+リリース日：2026年3月12日
+メッセージボード機能を追加</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -790,7 +918,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -816,13 +944,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -868,17 +989,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1160,40 +1290,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="59.75" customWidth="1"/>
-    <col min="3" max="3" width="57.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="75.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="59.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="57.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="75.5" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>57</v>
+      <c r="D1" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1201,602 +1331,854 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>56</v>
+      <c r="D3" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
+        <v>24</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>104</v>
+        <v>83</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>105</v>
+        <v>84</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>106</v>
+        <v>85</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>107</v>
+        <v>86</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" t="s">
-        <v>128</v>
+        <v>29</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" t="s">
-        <v>129</v>
+        <v>30</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" t="s">
-        <v>130</v>
+        <v>31</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D12" t="s">
-        <v>131</v>
+        <v>65</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" t="s">
-        <v>132</v>
+        <v>66</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" t="s">
-        <v>133</v>
+        <v>64</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" t="s">
-        <v>134</v>
+        <v>35</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>100</v>
-      </c>
-      <c r="B16" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16" t="s">
-        <v>135</v>
+        <v>70</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" t="s">
-        <v>136</v>
+        <v>8</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" t="s">
-        <v>137</v>
+      <c r="C18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" t="s">
-        <v>138</v>
+        <v>12</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" t="s">
-        <v>139</v>
+        <v>14</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" t="s">
-        <v>104</v>
+        <v>16</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" t="s">
-        <v>105</v>
+        <v>18</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" t="s">
-        <v>106</v>
+        <v>20</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" t="s">
-        <v>107</v>
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" t="s">
-        <v>108</v>
+      <c r="C25" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C26" t="s">
-        <v>149</v>
-      </c>
-      <c r="D26" t="s">
-        <v>149</v>
+      <c r="D26" s="6" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B27" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" t="s">
-        <v>39</v>
+      <c r="C27" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" t="s">
-        <v>109</v>
+        <v>37</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29" t="s">
-        <v>110</v>
+        <v>42</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" t="s">
-        <v>111</v>
+        <v>43</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" t="s">
-        <v>81</v>
-      </c>
-      <c r="C31" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" t="s">
-        <v>112</v>
+        <v>44</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" t="s">
-        <v>113</v>
+        <v>45</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>68</v>
-      </c>
-      <c r="B33" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="D33" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>69</v>
-      </c>
-      <c r="B34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34" t="s">
-        <v>77</v>
-      </c>
-      <c r="D34" t="s">
-        <v>115</v>
+        <v>50</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35" t="s">
-        <v>74</v>
-      </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35" t="s">
-        <v>116</v>
+        <v>51</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" t="s">
-        <v>79</v>
-      </c>
-      <c r="D36" t="s">
-        <v>117</v>
+        <v>52</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>82</v>
-      </c>
-      <c r="B37" t="s">
-        <v>84</v>
-      </c>
-      <c r="C37" t="s">
-        <v>86</v>
-      </c>
-      <c r="D37" t="s">
-        <v>118</v>
+        <v>58</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>83</v>
-      </c>
-      <c r="B38" t="s">
-        <v>85</v>
-      </c>
-      <c r="C38" t="s">
-        <v>87</v>
-      </c>
-      <c r="D38" t="s">
-        <v>119</v>
+        <v>59</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="60" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="56" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B43" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C43" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D39" t="s">
+      <c r="B44" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" ht="86.5" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B40" s="4" t="s">
+      <c r="C59" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C60" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="C61" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D41" s="2" t="s">
+      <c r="C62" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="106" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>161</v>
+      <c r="B63" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/cfg/excel/lang_cfg.xlsx
+++ b/cfg/excel/lang_cfg.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D92"/>
   <cols>
     <col min="1" max="1" width="31.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -1081,609 +1081,637 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>msg_form_title</v>
+        <v>tab_test</v>
       </c>
       <c r="B48" t="str">
-        <v>写下你的留言</v>
+        <v>基准测试</v>
       </c>
       <c r="C48" t="str">
-        <v>Leave a Message</v>
+        <v>Baseline Test</v>
       </c>
       <c r="D48" t="str">
-        <v>メッセージを書く</v>
+        <v>Baseline Test</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>msg_nickname_label</v>
+        <v>test_title</v>
       </c>
       <c r="B49" t="str">
-        <v>昵称</v>
+        <v>基准测试</v>
       </c>
       <c r="C49" t="str">
-        <v>Nickname</v>
+        <v>Baseline Test</v>
       </c>
       <c r="D49" t="str">
-        <v>ニックネーム</v>
+        <v>Baseline Test</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>msg_nickname_placeholder</v>
+        <v>msg_form_title</v>
       </c>
       <c r="B50" t="str">
-        <v>你的昵称</v>
+        <v>写下你的留言</v>
       </c>
       <c r="C50" t="str">
-        <v>Your nickname</v>
+        <v>Leave a Message</v>
       </c>
       <c r="D50" t="str">
-        <v>ニックネームを入力</v>
+        <v>メッセージを書く</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>msg_content_label</v>
+        <v>msg_nickname_label</v>
       </c>
       <c r="B51" t="str">
-        <v>留言内容</v>
+        <v>昵称</v>
       </c>
       <c r="C51" t="str">
-        <v>Message</v>
+        <v>Nickname</v>
       </c>
       <c r="D51" t="str">
-        <v>メッセージ</v>
+        <v>ニックネーム</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>msg_content_placeholder</v>
+        <v>msg_nickname_placeholder</v>
       </c>
       <c r="B52" t="str">
-        <v>写点什么吧…</v>
+        <v>你的昵称</v>
       </c>
       <c r="C52" t="str">
-        <v>Write something…</v>
+        <v>Your nickname</v>
       </c>
       <c r="D52" t="str">
-        <v>何か書いてみましょう…</v>
+        <v>ニックネームを入力</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>msg_submit_btn</v>
+        <v>msg_content_label</v>
       </c>
       <c r="B53" t="str">
-        <v>发送</v>
+        <v>留言内容</v>
       </c>
       <c r="C53" t="str">
-        <v>Send</v>
+        <v>Message</v>
       </c>
       <c r="D53" t="str">
-        <v>送信</v>
+        <v>メッセージ</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>msg_list_title</v>
+        <v>msg_content_placeholder</v>
       </c>
       <c r="B54" t="str">
-        <v>留言板（{0}）</v>
+        <v>写点什么吧…</v>
       </c>
       <c r="C54" t="str">
-        <v>Message Board ({0})</v>
+        <v>Write something…</v>
       </c>
       <c r="D54" t="str">
-        <v>メッセージボード（{0}）</v>
+        <v>何か書いてみましょう…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>msg_refresh_btn</v>
+        <v>msg_submit_btn</v>
       </c>
       <c r="B55" t="str">
-        <v>刷新</v>
+        <v>发送</v>
       </c>
       <c r="C55" t="str">
-        <v>Refresh</v>
+        <v>Send</v>
       </c>
       <c r="D55" t="str">
-        <v>更新</v>
+        <v>送信</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>msg_loading</v>
+        <v>msg_list_title</v>
       </c>
       <c r="B56" t="str">
-        <v>正在加载留言…</v>
+        <v>留言板（{0}）</v>
       </c>
       <c r="C56" t="str">
-        <v>Loading messages…</v>
+        <v>Message Board ({0})</v>
       </c>
       <c r="D56" t="str">
-        <v>メッセージを読み込んでいます…</v>
+        <v>メッセージボード（{0}）</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>msg_empty</v>
+        <v>msg_refresh_btn</v>
       </c>
       <c r="B57" t="str">
-        <v>暂无留言，和我说点什么！</v>
+        <v>刷新</v>
       </c>
       <c r="C57" t="str">
-        <v>No messages yet — say something!</v>
+        <v>Refresh</v>
       </c>
       <c r="D57" t="str">
-        <v>まだメッセージはありません。ぜひ一言どうぞ！</v>
+        <v>更新</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>msg_error</v>
+        <v>msg_loading</v>
       </c>
       <c r="B58" t="str">
-        <v>加载留言失败，请稍后再试。</v>
+        <v>正在加载留言…</v>
       </c>
       <c r="C58" t="str">
-        <v>Could not load messages. Try again later.</v>
+        <v>Loading messages…</v>
       </c>
       <c r="D58" t="str">
-        <v>メッセージを読み込めませんでした。後ほどお試しください。</v>
+        <v>メッセージを読み込んでいます…</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>msg_load_more</v>
+        <v>msg_empty</v>
       </c>
       <c r="B59" t="str">
-        <v>加载更多</v>
+        <v>暂无留言，和我说点什么！</v>
       </c>
       <c r="C59" t="str">
-        <v>Load more</v>
+        <v>No messages yet — say something!</v>
       </c>
       <c r="D59" t="str">
-        <v>もっと見る</v>
+        <v>まだメッセージはありません。ぜひ一言どうぞ！</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>msg_warn_nickname</v>
+        <v>msg_error</v>
       </c>
       <c r="B60" t="str">
-        <v>请输入昵称</v>
+        <v>加载留言失败，请稍后再试。</v>
       </c>
       <c r="C60" t="str">
-        <v>Please enter a nickname</v>
+        <v>Could not load messages. Try again later.</v>
       </c>
       <c r="D60" t="str">
-        <v>ニックネームを入力してください</v>
+        <v>メッセージを読み込めませんでした。後ほどお試しください。</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>msg_warn_content</v>
+        <v>msg_load_more</v>
       </c>
       <c r="B61" t="str">
-        <v>请输入留言内容</v>
+        <v>加载更多</v>
       </c>
       <c r="C61" t="str">
-        <v>Please enter a message</v>
+        <v>Load more</v>
       </c>
       <c r="D61" t="str">
-        <v>メッセージ内容を入力してください</v>
+        <v>もっと見る</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>msg_success_title</v>
+        <v>msg_warn_nickname</v>
       </c>
       <c r="B62" t="str">
-        <v>留言已发送！</v>
+        <v>请输入昵称</v>
       </c>
       <c r="C62" t="str">
-        <v>Message sent!</v>
+        <v>Please enter a nickname</v>
       </c>
       <c r="D62" t="str">
-        <v>送信完了！</v>
+        <v>ニックネームを入力してください</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>msg_submit_error</v>
+        <v>msg_warn_content</v>
       </c>
       <c r="B63" t="str">
-        <v>发送失败，请稍后再试</v>
+        <v>请输入留言内容</v>
       </c>
       <c r="C63" t="str">
-        <v>Failed to send. Please try again later.</v>
+        <v>Please enter a message</v>
       </c>
       <c r="D63" t="str">
-        <v>送信に失敗しました。後ほどもう一度お試しください。</v>
+        <v>メッセージ内容を入力してください</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>msg_reply_btn</v>
+        <v>msg_success_title</v>
       </c>
       <c r="B64" t="str">
-        <v>评论</v>
+        <v>留言已发送！</v>
       </c>
       <c r="C64" t="str">
-        <v>Reply</v>
+        <v>Message sent!</v>
       </c>
       <c r="D64" t="str">
-        <v>返信</v>
+        <v>送信完了！</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>msg_reply_submit_btn</v>
+        <v>msg_submit_error</v>
       </c>
       <c r="B65" t="str">
-        <v>发送评论</v>
+        <v>发送失败，请稍后再试</v>
       </c>
       <c r="C65" t="str">
-        <v>Send Reply</v>
+        <v>Failed to send. Please try again later.</v>
       </c>
       <c r="D65" t="str">
-        <v>返信を送信</v>
+        <v>送信に失敗しました。後ほどもう一度お試しください。</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>msg_reply_content_placeholder</v>
+        <v>msg_reply_btn</v>
       </c>
       <c r="B66" t="str">
-        <v>写下你的评论…</v>
+        <v>评论</v>
       </c>
       <c r="C66" t="str">
-        <v>Write your reply...</v>
+        <v>Reply</v>
       </c>
       <c r="D66" t="str">
-        <v>返信を書いてください…</v>
+        <v>返信</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>msg_reply_success</v>
+        <v>msg_reply_submit_btn</v>
       </c>
       <c r="B67" t="str">
-        <v>评论已发送！</v>
+        <v>发送评论</v>
       </c>
       <c r="C67" t="str">
-        <v>Reply sent!</v>
+        <v>Send Reply</v>
       </c>
       <c r="D67" t="str">
-        <v>返信を送信しました！</v>
+        <v>返信を送信</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>msg_reply_reply_btn</v>
+        <v>msg_reply_content_placeholder</v>
       </c>
       <c r="B68" t="str">
-        <v>回复</v>
+        <v>写下你的评论…</v>
       </c>
       <c r="C68" t="str">
-        <v>Reply</v>
+        <v>Write your reply...</v>
       </c>
       <c r="D68" t="str">
-        <v>返信</v>
+        <v>返信を書いてください…</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>msg_replying_to</v>
+        <v>msg_reply_success</v>
       </c>
       <c r="B69" t="str">
-        <v>回复</v>
+        <v>评论已发送！</v>
       </c>
       <c r="C69" t="str">
-        <v>Replying to</v>
+        <v>Reply sent!</v>
       </c>
       <c r="D69" t="str">
-        <v>返信先：</v>
+        <v>返信を送信しました！</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>msg_reply_cancel_btn</v>
+        <v>msg_reply_reply_btn</v>
       </c>
       <c r="B70" t="str">
-        <v>取消</v>
+        <v>回复</v>
       </c>
       <c r="C70" t="str">
-        <v>Cancel</v>
+        <v>Reply</v>
       </c>
       <c r="D70" t="str">
-        <v>キャンセル</v>
+        <v>返信</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>msg_time_minutes_ago</v>
+        <v>msg_replying_to</v>
       </c>
       <c r="B71" t="str">
-        <v>{0}分钟前</v>
+        <v>回复</v>
       </c>
       <c r="C71" t="str">
-        <v>{0}m ago</v>
+        <v>Replying to</v>
       </c>
       <c r="D71" t="str">
-        <v>{0}分前</v>
+        <v>返信先：</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>msg_time_hours_ago</v>
+        <v>msg_reply_cancel_btn</v>
       </c>
       <c r="B72" t="str">
-        <v>{0}小时前</v>
+        <v>取消</v>
       </c>
       <c r="C72" t="str">
-        <v>{0}h ago</v>
+        <v>Cancel</v>
       </c>
       <c r="D72" t="str">
-        <v>{0}時間前</v>
+        <v>キャンセル</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>post_publish_date</v>
+        <v>msg_time_minutes_ago</v>
       </c>
       <c r="B73" t="str">
-        <v>发布时间：{0}</v>
+        <v>{0}分钟前</v>
       </c>
       <c r="C73" t="str">
-        <v>Published: {0}</v>
+        <v>{0}m ago</v>
       </c>
       <c r="D73" t="str">
-        <v>公開日：{0}</v>
+        <v>{0}分前</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>game_quality_6</v>
+        <v>msg_time_hours_ago</v>
       </c>
       <c r="B74" t="str">
-        <v>大师之作</v>
+        <v>{0}小时前</v>
       </c>
       <c r="C74" t="str">
-        <v>Masterpiece</v>
+        <v>{0}h ago</v>
       </c>
       <c r="D74" t="str">
-        <v>傑作</v>
+        <v>{0}時間前</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>game_quality_5</v>
+        <v>post_publish_date</v>
       </c>
       <c r="B75" t="str">
-        <v>奇佳</v>
+        <v>发布时间：{0}</v>
       </c>
       <c r="C75" t="str">
-        <v>Outstanding</v>
+        <v>Published: {0}</v>
       </c>
       <c r="D75" t="str">
-        <v>秀逸</v>
+        <v>公開日：{0}</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>game_quality_4</v>
+        <v>game_quality_6</v>
       </c>
       <c r="B76" t="str">
-        <v>卓越</v>
+        <v>大师之作</v>
       </c>
       <c r="C76" t="str">
-        <v>Excellent</v>
+        <v>Masterpiece</v>
       </c>
       <c r="D76" t="str">
-        <v>卓越</v>
+        <v>傑作</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>game_quality_3</v>
+        <v>game_quality_5</v>
       </c>
       <c r="B77" t="str">
-        <v>优秀</v>
+        <v>奇佳</v>
       </c>
       <c r="C77" t="str">
-        <v>Great</v>
+        <v>Outstanding</v>
       </c>
       <c r="D77" t="str">
-        <v>優秀</v>
+        <v>秀逸</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>game_quality_2</v>
+        <v>game_quality_4</v>
       </c>
       <c r="B78" t="str">
-        <v>尚可</v>
+        <v>卓越</v>
       </c>
       <c r="C78" t="str">
-        <v>Decent</v>
+        <v>Excellent</v>
       </c>
       <c r="D78" t="str">
-        <v>まずまず</v>
+        <v>卓越</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>game_quality_1</v>
+        <v>game_quality_3</v>
       </c>
       <c r="B79" t="str">
-        <v>平庸</v>
+        <v>优秀</v>
       </c>
       <c r="C79" t="str">
-        <v>Mediocre</v>
+        <v>Great</v>
       </c>
       <c r="D79" t="str">
-        <v>平凡</v>
+        <v>優秀</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>game_type_1</v>
+        <v>game_quality_2</v>
       </c>
       <c r="B80" t="str">
-        <v>竞技类</v>
+        <v>尚可</v>
       </c>
       <c r="C80" t="str">
-        <v>Competitive</v>
+        <v>Decent</v>
       </c>
       <c r="D80" t="str">
-        <v>対戦</v>
+        <v>まずまず</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>game_type_2</v>
+        <v>game_quality_1</v>
       </c>
       <c r="B81" t="str">
-        <v>动作&amp;沙盒类</v>
+        <v>平庸</v>
       </c>
       <c r="C81" t="str">
-        <v>Action &amp; Sandbox</v>
+        <v>Mediocre</v>
       </c>
       <c r="D81" t="str">
-        <v>アクション＆サンドボックス</v>
+        <v>平凡</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>game_type_3</v>
+        <v>game_type_1</v>
       </c>
       <c r="B82" t="str">
-        <v>模拟经营类</v>
+        <v>竞技类</v>
       </c>
       <c r="C82" t="str">
-        <v>Simulation &amp; Management</v>
+        <v>Competitive</v>
       </c>
       <c r="D82" t="str">
-        <v>シミュレーション＆経営</v>
+        <v>対戦</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>game_type_4</v>
+        <v>game_type_2</v>
       </c>
       <c r="B83" t="str">
-        <v>独立游戏&amp;Roguelike</v>
+        <v>动作&amp;沙盒类</v>
       </c>
       <c r="C83" t="str">
-        <v>Indie &amp; Roguelike</v>
+        <v>Action &amp; Sandbox</v>
       </c>
       <c r="D83" t="str">
-        <v>インディー＆ローグライク</v>
+        <v>アクション＆サンドボックス</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>game_type_5</v>
+        <v>game_type_3</v>
       </c>
       <c r="B84" t="str">
-        <v>RTS</v>
+        <v>模拟经营类</v>
       </c>
       <c r="C84" t="str">
-        <v>RTS</v>
+        <v>Simulation &amp; Management</v>
       </c>
       <c r="D84" t="str">
-        <v>RTS</v>
+        <v>シミュレーション＆経営</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>game_type_6</v>
+        <v>game_type_4</v>
       </c>
       <c r="B85" t="str">
-        <v>集换式卡牌&amp;自走棋</v>
+        <v>独立游戏&amp;Roguelike</v>
       </c>
       <c r="C85" t="str">
-        <v>TCG &amp; Auto Chess</v>
+        <v>Indie &amp; Roguelike</v>
       </c>
       <c r="D85" t="str">
-        <v>TCG＆オートチェス</v>
+        <v>インディー＆ローグライク</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>game_type_7</v>
+        <v>game_type_5</v>
       </c>
       <c r="B86" t="str">
-        <v>手游</v>
+        <v>RTS</v>
       </c>
       <c r="C86" t="str">
-        <v>Mobile Games</v>
+        <v>RTS</v>
       </c>
       <c r="D86" t="str">
-        <v>モバイルゲーム</v>
+        <v>RTS</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>game_type_8</v>
+        <v>game_type_6</v>
       </c>
       <c r="B87" t="str">
-        <v>其他网游</v>
+        <v>集换式卡牌&amp;自走棋</v>
       </c>
       <c r="C87" t="str">
-        <v>Other Online Games</v>
+        <v>TCG &amp; Auto Chess</v>
       </c>
       <c r="D87" t="str">
-        <v>その他のオンラインゲーム</v>
+        <v>TCG＆オートチェス</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>game_no_series</v>
+        <v>game_type_7</v>
       </c>
       <c r="B88" t="str">
-        <v>无系列</v>
+        <v>手游</v>
       </c>
       <c r="C88" t="str">
-        <v>No Series</v>
+        <v>Mobile Games</v>
       </c>
       <c r="D88" t="str">
-        <v>シリーズなし</v>
+        <v>モバイルゲーム</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>game_unknown_quality</v>
+        <v>game_type_8</v>
       </c>
       <c r="B89" t="str">
-        <v>未定义评级（{0}）</v>
+        <v>其他网游</v>
       </c>
       <c r="C89" t="str">
-        <v>Undefined Rating ({0})</v>
+        <v>Other Online Games</v>
       </c>
       <c r="D89" t="str">
-        <v>未定義の評価（{0}）</v>
+        <v>その他のオンラインゲーム</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
+        <v>game_no_series</v>
+      </c>
+      <c r="B90" t="str">
+        <v>无系列</v>
+      </c>
+      <c r="C90" t="str">
+        <v>No Series</v>
+      </c>
+      <c r="D90" t="str">
+        <v>シリーズなし</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>game_unknown_quality</v>
+      </c>
+      <c r="B91" t="str">
+        <v>未定义评级（{0}）</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Undefined Rating ({0})</v>
+      </c>
+      <c r="D91" t="str">
+        <v>未定義の評価（{0}）</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
         <v>game_load_error</v>
       </c>
-      <c r="B90" t="str">
+      <c r="B92" t="str">
         <v>数据加载失败，请刷新页面</v>
       </c>
-      <c r="C90" t="str">
+      <c r="C92" t="str">
         <v>Failed to load data. Please refresh the page.</v>
       </c>
-      <c r="D90" t="str">
+      <c r="D92" t="str">
         <v>データの読み込みに失敗しました。ページを更新してください。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D90"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D92"/>
   </ignoredErrors>
 </worksheet>
 </file>